--- a/workpapers/Northstar_ITGC_Audit_Workpapers_and_Remediation_Tracker.xlsx
+++ b/workpapers/Northstar_ITGC_Audit_Workpapers_and_Remediation_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9284898eb17b6c96/Arizona Online/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_56CD2AFDD719852AC83101F3DDDC26D3D38CDE7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E11C7D73-4D56-4629-986B-5B5EE920C9DE}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_56CD2AFDD719852AC83101F3DDDC26D3D38CDE7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5530F9EB-AA37-43DC-AEA6-AA696E3AE6AB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Audit Dashboard" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Terminations!$A$1:$J$13</definedName>
   </definedNames>
   <calcPr calcId="191029" forceFullCalc="1"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -62,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="962">
   <si>
     <t>NORTHSTAR SERVICES — ITGC AUDIT DASHBOARD</t>
   </si>
@@ -2936,6 +2935,18 @@
   </si>
   <si>
     <t>2026-09-10 09:25</t>
+  </si>
+  <si>
+    <t>Exceptions &amp; Gaps</t>
+  </si>
+  <si>
+    <t>Summary of selected preliminary exceptions and evidence gaps. This is not a complete record of all planned sample tests; refer to WP-001 through WP-005 for detailed results.</t>
+  </si>
+  <si>
+    <t>Planned Samples</t>
+  </si>
+  <si>
+    <t>WP-001: 10; WP-002: 10; WP-003: 10; WP-004: 6; WP-005: 10. Total planned sample: 46.</t>
   </si>
 </sst>
 </file>
@@ -8893,7 +8904,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -8960,6 +8971,22 @@
       </c>
       <c r="B8" s="2" t="s">
         <v>462</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>961</v>
       </c>
     </row>
   </sheetData>
